--- a/Modified Dataset/Events_Data_1April2013.xlsx
+++ b/Modified Dataset/Events_Data_1April2013.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arnavgupta/Documents/Arnav/Hackathons/DecodeX/Modified Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3A75FA96-224F-D548-8BCD-C5D92C0008C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C907860-42E8-C34D-8112-EFB7CEA6A01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1080" yWindow="1140" windowWidth="27640" windowHeight="16540" xr2:uid="{9D46C0F9-12FB-2844-AC27-29D70BA9F9B5}"/>
   </bookViews>
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="133">
-  <si>
-    <t>Date</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="133">
   <si>
     <t>Event_Name</t>
   </si>
@@ -419,6 +416,9 @@
   </si>
   <si>
     <t>Lockdown Phase 4 (18th May – 31st May)</t>
+  </si>
+  <si>
+    <t>DATE</t>
   </si>
 </sst>
 </file>
@@ -1280,21 +1280,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB10D5D-7D94-734B-A96F-68EB76319A4B}">
-  <dimension ref="A1:D527"/>
+  <dimension ref="A1:D490"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>132</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -1302,7 +1302,7 @@
         <v>41375</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C2">
         <v>1</v>
@@ -1313,7 +1313,7 @@
         <v>41378</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -1324,7 +1324,7 @@
         <v>41383</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1335,7 +1335,7 @@
         <v>41387</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1346,7 +1346,7 @@
         <v>41389</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1357,7 +1357,7 @@
         <v>41395</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>1</v>
@@ -1368,7 +1368,7 @@
         <v>41419</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1379,7 +1379,7 @@
         <v>41432</v>
       </c>
       <c r="B9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C9">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>41434</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10">
         <v>1</v>
@@ -1401,7 +1401,7 @@
         <v>41435</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -1412,7 +1412,7 @@
         <v>41441</v>
       </c>
       <c r="B12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -1423,7 +1423,7 @@
         <v>41449</v>
       </c>
       <c r="B13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1434,7 +1434,7 @@
         <v>41450</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1445,7 +1445,7 @@
         <v>41463</v>
       </c>
       <c r="B15" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1456,7 +1456,7 @@
         <v>41464</v>
       </c>
       <c r="B16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C16">
         <v>1</v>
@@ -1467,7 +1467,7 @@
         <v>41467</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>41472</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1489,7 +1489,7 @@
         <v>41478</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>41495</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>1</v>
@@ -1511,7 +1511,7 @@
         <v>41501</v>
       </c>
       <c r="B21" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C21">
         <v>1</v>
@@ -1522,7 +1522,7 @@
         <v>41504</v>
       </c>
       <c r="B22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C22">
         <v>1</v>
@@ -1533,7 +1533,7 @@
         <v>41506</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23">
         <v>1</v>
@@ -1544,7 +1544,7 @@
         <v>41515</v>
       </c>
       <c r="B24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C24">
         <v>1</v>
@@ -1555,7 +1555,7 @@
         <v>41526</v>
       </c>
       <c r="B25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1566,7 +1566,7 @@
         <v>41527</v>
       </c>
       <c r="B26" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1577,7 +1577,7 @@
         <v>41528</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C27">
         <v>0</v>
@@ -1588,7 +1588,7 @@
         <v>41529</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1599,7 +1599,7 @@
         <v>41530</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29">
         <v>0</v>
@@ -1610,7 +1610,7 @@
         <v>41531</v>
       </c>
       <c r="B30" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1621,7 +1621,7 @@
         <v>41532</v>
       </c>
       <c r="B31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31">
         <v>0</v>
@@ -1632,7 +1632,7 @@
         <v>41532</v>
       </c>
       <c r="B32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>0</v>
@@ -1643,7 +1643,7 @@
         <v>41533</v>
       </c>
       <c r="B33" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C33">
         <v>0</v>
@@ -1654,7 +1654,7 @@
         <v>41534</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1665,7 +1665,7 @@
         <v>41535</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C35">
         <v>1</v>
@@ -1676,7 +1676,7 @@
         <v>41536</v>
       </c>
       <c r="B36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C36">
         <v>0</v>
@@ -1687,7 +1687,7 @@
         <v>41541</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1698,7 +1698,7 @@
         <v>41549</v>
       </c>
       <c r="B38" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C38">
         <v>1</v>
@@ -1709,7 +1709,7 @@
         <v>41552</v>
       </c>
       <c r="B39" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C39">
         <v>0</v>
@@ -1720,7 +1720,7 @@
         <v>41553</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1731,7 +1731,7 @@
         <v>41554</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1742,7 +1742,7 @@
         <v>41555</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C42">
         <v>0</v>
@@ -1753,7 +1753,7 @@
         <v>41556</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1764,7 +1764,7 @@
         <v>41557</v>
       </c>
       <c r="B44" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>41558</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1786,7 +1786,7 @@
         <v>41559</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1797,7 +1797,7 @@
         <v>41560</v>
       </c>
       <c r="B47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C47">
         <v>1</v>
@@ -1808,7 +1808,7 @@
         <v>41563</v>
       </c>
       <c r="B48" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C48">
         <v>1</v>
@@ -1819,7 +1819,7 @@
         <v>41579</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1830,7 +1830,7 @@
         <v>41581</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50">
         <v>1</v>
@@ -1841,7 +1841,7 @@
         <v>41582</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51">
         <v>1</v>
@@ -1852,7 +1852,7 @@
         <v>41583</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C52">
         <v>1</v>
@@ -1863,7 +1863,7 @@
         <v>41592</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1874,7 +1874,7 @@
         <v>41595</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1885,7 +1885,7 @@
         <v>41624</v>
       </c>
       <c r="B55" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>41633</v>
       </c>
       <c r="B56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -1907,7 +1907,7 @@
         <v>41640</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -1918,7 +1918,7 @@
         <v>41653</v>
       </c>
       <c r="B58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C58">
         <v>1</v>
@@ -1929,7 +1929,7 @@
         <v>41653</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C59">
         <v>1</v>
@@ -1940,7 +1940,7 @@
         <v>41665</v>
       </c>
       <c r="B60" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C60">
         <v>1</v>
@@ -1951,7 +1951,7 @@
         <v>41689</v>
       </c>
       <c r="B61" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -1962,7 +1962,7 @@
         <v>41697</v>
       </c>
       <c r="B62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C62">
         <v>1</v>
@@ -1973,7 +1973,7 @@
         <v>41715</v>
       </c>
       <c r="B63" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1984,7 +1984,7 @@
         <v>41729</v>
       </c>
       <c r="B64" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C64">
         <v>1</v>
@@ -1995,7 +1995,7 @@
         <v>41737</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2006,7 +2006,7 @@
         <v>41742</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2017,7 +2017,7 @@
         <v>41743</v>
       </c>
       <c r="B67" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C67">
         <v>1</v>
@@ -2028,7 +2028,7 @@
         <v>41744</v>
       </c>
       <c r="B68" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>41747</v>
       </c>
       <c r="B69" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2050,7 +2050,7 @@
         <v>41753</v>
       </c>
       <c r="B70" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2061,7 +2061,7 @@
         <v>41760</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C71">
         <v>1</v>
@@ -2072,7 +2072,7 @@
         <v>41773</v>
       </c>
       <c r="B72" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2083,7 +2083,7 @@
         <v>41822</v>
       </c>
       <c r="B73" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C73">
         <v>1</v>
@@ -2094,7 +2094,7 @@
         <v>41827</v>
       </c>
       <c r="B74" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2105,7 +2105,7 @@
         <v>41829</v>
       </c>
       <c r="B75" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2116,7 +2116,7 @@
         <v>41831</v>
       </c>
       <c r="B76" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>41832</v>
       </c>
       <c r="B77" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>41835</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C78">
         <v>1</v>
@@ -2149,7 +2149,7 @@
         <v>41836</v>
       </c>
       <c r="B79" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2160,7 +2160,7 @@
         <v>41847</v>
       </c>
       <c r="B80" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C80">
         <v>1</v>
@@ -2171,7 +2171,7 @@
         <v>41848</v>
       </c>
       <c r="B81" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2182,7 +2182,7 @@
         <v>41849</v>
       </c>
       <c r="B82" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C82">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         <v>41849</v>
       </c>
       <c r="B83" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C83">
         <v>1</v>
@@ -2204,7 +2204,7 @@
         <v>41850</v>
       </c>
       <c r="B84" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C84">
         <v>0</v>
@@ -2215,7 +2215,7 @@
         <v>41852</v>
       </c>
       <c r="B85" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C85">
         <v>1</v>
@@ -2226,7 +2226,7 @@
         <v>41866</v>
       </c>
       <c r="B86" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C86">
         <v>1</v>
@@ -2237,7 +2237,7 @@
         <v>41869</v>
       </c>
       <c r="B87" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C87">
         <v>1</v>
@@ -2248,7 +2248,7 @@
         <v>41869</v>
       </c>
       <c r="B88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C88">
         <v>1</v>
@@ -2259,7 +2259,7 @@
         <v>41880</v>
       </c>
       <c r="B89" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -2270,7 +2270,7 @@
         <v>41881</v>
       </c>
       <c r="B90" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C90">
         <v>0</v>
@@ -2281,7 +2281,7 @@
         <v>41882</v>
       </c>
       <c r="B91" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -2292,7 +2292,7 @@
         <v>41882</v>
       </c>
       <c r="B92" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2303,7 +2303,7 @@
         <v>41883</v>
       </c>
       <c r="B93" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2314,7 +2314,7 @@
         <v>41883</v>
       </c>
       <c r="B94" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2325,7 +2325,7 @@
         <v>41884</v>
       </c>
       <c r="B95" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C95">
         <v>0</v>
@@ -2336,7 +2336,7 @@
         <v>41884</v>
       </c>
       <c r="B96" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -2347,7 +2347,7 @@
         <v>41885</v>
       </c>
       <c r="B97" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C97">
         <v>0</v>
@@ -2358,7 +2358,7 @@
         <v>41886</v>
       </c>
       <c r="B98" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -2369,7 +2369,7 @@
         <v>41887</v>
       </c>
       <c r="B99" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C99">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         <v>41888</v>
       </c>
       <c r="B100" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C100">
         <v>0</v>
@@ -2391,7 +2391,7 @@
         <v>41889</v>
       </c>
       <c r="B101" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -2402,7 +2402,7 @@
         <v>41890</v>
       </c>
       <c r="B102" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -2413,7 +2413,7 @@
         <v>41907</v>
       </c>
       <c r="B103" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -2424,7 +2424,7 @@
         <v>41908</v>
       </c>
       <c r="B104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C104">
         <v>0</v>
@@ -2435,7 +2435,7 @@
         <v>41909</v>
       </c>
       <c r="B105" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C105">
         <v>0</v>
@@ -2446,7 +2446,7 @@
         <v>41910</v>
       </c>
       <c r="B106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>41911</v>
       </c>
       <c r="B107" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C107">
         <v>0</v>
@@ -2468,7 +2468,7 @@
         <v>41912</v>
       </c>
       <c r="B108" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C108">
         <v>0</v>
@@ -2479,7 +2479,7 @@
         <v>41913</v>
       </c>
       <c r="B109" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C109">
         <v>0</v>
@@ -2490,7 +2490,7 @@
         <v>41914</v>
       </c>
       <c r="B110" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C110">
         <v>1</v>
@@ -2501,7 +2501,7 @@
         <v>41914</v>
       </c>
       <c r="B111" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -2512,7 +2512,7 @@
         <v>41915</v>
       </c>
       <c r="B112" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C112">
         <v>1</v>
@@ -2523,7 +2523,7 @@
         <v>41917</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -2534,7 +2534,7 @@
         <v>41927</v>
       </c>
       <c r="B114" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C114">
         <v>0</v>
@@ -2545,7 +2545,7 @@
         <v>41933</v>
       </c>
       <c r="B115" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C115">
         <v>0</v>
@@ -2556,7 +2556,7 @@
         <v>41935</v>
       </c>
       <c r="B116" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -2567,7 +2567,7 @@
         <v>41936</v>
       </c>
       <c r="B117" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -2578,7 +2578,7 @@
         <v>41937</v>
       </c>
       <c r="B118" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -2589,7 +2589,7 @@
         <v>41947</v>
       </c>
       <c r="B119" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -2600,7 +2600,7 @@
         <v>41949</v>
       </c>
       <c r="B120" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -2611,7 +2611,7 @@
         <v>41979</v>
       </c>
       <c r="B121" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -2622,7 +2622,7 @@
         <v>41998</v>
       </c>
       <c r="B122" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C122">
         <v>1</v>
@@ -2633,7 +2633,7 @@
         <v>42005</v>
       </c>
       <c r="B123" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C123">
         <v>1</v>
@@ -2644,7 +2644,7 @@
         <v>42008</v>
       </c>
       <c r="B124" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C124">
         <v>1</v>
@@ -2655,7 +2655,7 @@
         <v>42019</v>
       </c>
       <c r="B125" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C125">
         <v>1</v>
@@ -2666,7 +2666,7 @@
         <v>42030</v>
       </c>
       <c r="B126" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C126">
         <v>1</v>
@@ -2677,7 +2677,7 @@
         <v>42052</v>
       </c>
       <c r="B127" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C127">
         <v>1</v>
@@ -2688,7 +2688,7 @@
         <v>42054</v>
       </c>
       <c r="B128" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C128">
         <v>0</v>
@@ -2699,7 +2699,7 @@
         <v>42069</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C129">
         <v>1</v>
@@ -2710,7 +2710,7 @@
         <v>42084</v>
       </c>
       <c r="B130" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C130">
         <v>1</v>
@@ -2721,7 +2721,7 @@
         <v>42091</v>
       </c>
       <c r="B131" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -2732,7 +2732,7 @@
         <v>42096</v>
       </c>
       <c r="B132" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C132">
         <v>0</v>
@@ -2743,7 +2743,7 @@
         <v>42097</v>
       </c>
       <c r="B133" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C133">
         <v>0</v>
@@ -2754,7 +2754,7 @@
         <v>42098</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C134">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         <v>42108</v>
       </c>
       <c r="B135" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C135">
         <v>1</v>
@@ -2776,7 +2776,7 @@
         <v>42125</v>
       </c>
       <c r="B136" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C136">
         <v>1</v>
@@ -2787,7 +2787,7 @@
         <v>42128</v>
       </c>
       <c r="B137" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C137">
         <v>0</v>
@@ -2798,13 +2798,13 @@
         <v>42174</v>
       </c>
       <c r="B138" t="s">
+        <v>57</v>
+      </c>
+      <c r="C138">
+        <v>0</v>
+      </c>
+      <c r="D138" t="s">
         <v>58</v>
-      </c>
-      <c r="C138">
-        <v>0</v>
-      </c>
-      <c r="D138" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
@@ -2812,7 +2812,7 @@
         <v>42203</v>
       </c>
       <c r="B139" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C139">
         <v>1</v>
@@ -2823,7 +2823,7 @@
         <v>42231</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C140">
         <v>1</v>
@@ -2834,7 +2834,7 @@
         <v>42234</v>
       </c>
       <c r="B141" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C141">
         <v>1</v>
@@ -2845,7 +2845,7 @@
         <v>42245</v>
       </c>
       <c r="B142" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C142">
         <v>1</v>
@@ -2856,7 +2856,7 @@
         <v>42253</v>
       </c>
       <c r="B143" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C143">
         <v>1</v>
@@ -2867,7 +2867,7 @@
         <v>42264</v>
       </c>
       <c r="B144" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -2878,7 +2878,7 @@
         <v>42265</v>
       </c>
       <c r="B145" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C145">
         <v>0</v>
@@ -2889,7 +2889,7 @@
         <v>42266</v>
       </c>
       <c r="B146" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -2900,7 +2900,7 @@
         <v>42267</v>
       </c>
       <c r="B147" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C147">
         <v>0</v>
@@ -2911,7 +2911,7 @@
         <v>42268</v>
       </c>
       <c r="B148" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C148">
         <v>0</v>
@@ -2922,7 +2922,7 @@
         <v>42269</v>
       </c>
       <c r="B149" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C149">
         <v>0</v>
@@ -2933,7 +2933,7 @@
         <v>42270</v>
       </c>
       <c r="B150" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C150">
         <v>0</v>
@@ -2944,7 +2944,7 @@
         <v>42271</v>
       </c>
       <c r="B151" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -2955,7 +2955,7 @@
         <v>42271</v>
       </c>
       <c r="B152" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C152">
         <v>0</v>
@@ -2966,7 +2966,7 @@
         <v>42272</v>
       </c>
       <c r="B153" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C153">
         <v>0</v>
@@ -2977,7 +2977,7 @@
         <v>42273</v>
       </c>
       <c r="B154" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C154">
         <v>0</v>
@@ -2988,7 +2988,7 @@
         <v>42274</v>
       </c>
       <c r="B155" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C155">
         <v>1</v>
@@ -2999,7 +2999,7 @@
         <v>42279</v>
       </c>
       <c r="B156" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C156">
         <v>1</v>
@@ -3010,7 +3010,7 @@
         <v>42290</v>
       </c>
       <c r="B157" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C157">
         <v>0</v>
@@ -3021,7 +3021,7 @@
         <v>42291</v>
       </c>
       <c r="B158" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C158">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>42292</v>
       </c>
       <c r="B159" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C159">
         <v>0</v>
@@ -3043,7 +3043,7 @@
         <v>42293</v>
       </c>
       <c r="B160" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C160">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>42294</v>
       </c>
       <c r="B161" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -3065,7 +3065,7 @@
         <v>42295</v>
       </c>
       <c r="B162" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C162">
         <v>0</v>
@@ -3076,7 +3076,7 @@
         <v>42296</v>
       </c>
       <c r="B163" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C163">
         <v>0</v>
@@ -3087,7 +3087,7 @@
         <v>42297</v>
       </c>
       <c r="B164" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C164">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>42298</v>
       </c>
       <c r="B165" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C165">
         <v>0</v>
@@ -3109,7 +3109,7 @@
         <v>42299</v>
       </c>
       <c r="B166" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C166">
         <v>1</v>
@@ -3120,7 +3120,7 @@
         <v>42301</v>
       </c>
       <c r="B167" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C167">
         <v>1</v>
@@ -3131,7 +3131,7 @@
         <v>42317</v>
       </c>
       <c r="B168" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C168">
         <v>0</v>
@@ -3142,7 +3142,7 @@
         <v>42319</v>
       </c>
       <c r="B169" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C169">
         <v>1</v>
@@ -3153,7 +3153,7 @@
         <v>42320</v>
       </c>
       <c r="B170" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C170">
         <v>1</v>
@@ -3164,7 +3164,7 @@
         <v>42321</v>
       </c>
       <c r="B171" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C171">
         <v>1</v>
@@ -3175,7 +3175,7 @@
         <v>42333</v>
       </c>
       <c r="B172" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C172">
         <v>1</v>
@@ -3186,7 +3186,7 @@
         <v>42362</v>
       </c>
       <c r="B173" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -3197,7 +3197,7 @@
         <v>42363</v>
       </c>
       <c r="B174" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C174">
         <v>1</v>
@@ -3208,7 +3208,7 @@
         <v>42370</v>
       </c>
       <c r="B175" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C175">
         <v>1</v>
@@ -3219,7 +3219,7 @@
         <v>42384</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C176">
         <v>1</v>
@@ -3230,7 +3230,7 @@
         <v>42395</v>
       </c>
       <c r="B177" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C177">
         <v>1</v>
@@ -3241,7 +3241,7 @@
         <v>42419</v>
       </c>
       <c r="B178" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C178">
         <v>0</v>
@@ -3252,7 +3252,7 @@
         <v>42436</v>
       </c>
       <c r="B179" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C179">
         <v>1</v>
@@ -3263,7 +3263,7 @@
         <v>42453</v>
       </c>
       <c r="B180" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C180">
         <v>1</v>
@@ -3274,7 +3274,7 @@
         <v>42454</v>
       </c>
       <c r="B181" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -3285,7 +3285,7 @@
         <v>42468</v>
       </c>
       <c r="B182" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C182">
         <v>1</v>
@@ -3296,7 +3296,7 @@
         <v>42474</v>
       </c>
       <c r="B183" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C183">
         <v>1</v>
@@ -3307,7 +3307,7 @@
         <v>42475</v>
       </c>
       <c r="B184" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C184">
         <v>0</v>
@@ -3318,7 +3318,7 @@
         <v>42479</v>
       </c>
       <c r="B185" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C185">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>42482</v>
       </c>
       <c r="B186" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -3340,7 +3340,7 @@
         <v>42491</v>
       </c>
       <c r="B187" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C187">
         <v>1</v>
@@ -3351,7 +3351,7 @@
         <v>42511</v>
       </c>
       <c r="B188" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -3362,7 +3362,7 @@
         <v>42558</v>
       </c>
       <c r="B189" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C189">
         <v>1</v>
@@ -3373,13 +3373,13 @@
         <v>42582</v>
       </c>
       <c r="B190" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C190">
         <v>0</v>
       </c>
       <c r="D190" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
@@ -3387,7 +3387,7 @@
         <v>42597</v>
       </c>
       <c r="B191" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C191">
         <v>1</v>
@@ -3398,7 +3398,7 @@
         <v>42599</v>
       </c>
       <c r="B192" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C192">
         <v>1</v>
@@ -3409,7 +3409,7 @@
         <v>42600</v>
       </c>
       <c r="B193" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C193">
         <v>1</v>
@@ -3420,7 +3420,7 @@
         <v>42607</v>
       </c>
       <c r="B194" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C194">
         <v>1</v>
@@ -3431,7 +3431,7 @@
         <v>42618</v>
       </c>
       <c r="B195" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C195">
         <v>1</v>
@@ -3442,7 +3442,7 @@
         <v>42619</v>
       </c>
       <c r="B196" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         <v>42620</v>
       </c>
       <c r="B197" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C197">
         <v>0</v>
@@ -3464,7 +3464,7 @@
         <v>42621</v>
       </c>
       <c r="B198" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C198">
         <v>0</v>
@@ -3475,7 +3475,7 @@
         <v>42622</v>
       </c>
       <c r="B199" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C199">
         <v>0</v>
@@ -3486,7 +3486,7 @@
         <v>42623</v>
       </c>
       <c r="B200" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C200">
         <v>0</v>
@@ -3497,7 +3497,7 @@
         <v>42624</v>
       </c>
       <c r="B201" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -3508,7 +3508,7 @@
         <v>42625</v>
       </c>
       <c r="B202" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C202">
         <v>0</v>
@@ -3519,7 +3519,7 @@
         <v>42626</v>
       </c>
       <c r="B203" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C203">
         <v>1</v>
@@ -3530,7 +3530,7 @@
         <v>42626</v>
       </c>
       <c r="B204" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C204">
         <v>0</v>
@@ -3541,7 +3541,7 @@
         <v>42627</v>
       </c>
       <c r="B205" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C205">
         <v>0</v>
@@ -3552,7 +3552,7 @@
         <v>42628</v>
       </c>
       <c r="B206" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C206">
         <v>1</v>
@@ -3563,7 +3563,7 @@
         <v>42644</v>
       </c>
       <c r="B207" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C207">
         <v>0</v>
@@ -3574,7 +3574,7 @@
         <v>42645</v>
       </c>
       <c r="B208" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C208">
         <v>1</v>
@@ -3585,7 +3585,7 @@
         <v>42645</v>
       </c>
       <c r="B209" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C209">
         <v>0</v>
@@ -3596,7 +3596,7 @@
         <v>42646</v>
       </c>
       <c r="B210" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C210">
         <v>0</v>
@@ -3607,7 +3607,7 @@
         <v>42647</v>
       </c>
       <c r="B211" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -3618,7 +3618,7 @@
         <v>42648</v>
       </c>
       <c r="B212" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C212">
         <v>0</v>
@@ -3629,7 +3629,7 @@
         <v>42649</v>
       </c>
       <c r="B213" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C213">
         <v>0</v>
@@ -3640,7 +3640,7 @@
         <v>42650</v>
       </c>
       <c r="B214" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C214">
         <v>0</v>
@@ -3651,7 +3651,7 @@
         <v>42651</v>
       </c>
       <c r="B215" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C215">
         <v>0</v>
@@ -3662,7 +3662,7 @@
         <v>42652</v>
       </c>
       <c r="B216" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -3673,7 +3673,7 @@
         <v>42653</v>
       </c>
       <c r="B217" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C217">
         <v>0</v>
@@ -3684,7 +3684,7 @@
         <v>42654</v>
       </c>
       <c r="B218" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C218">
         <v>1</v>
@@ -3695,7 +3695,7 @@
         <v>42655</v>
       </c>
       <c r="B219" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C219">
         <v>1</v>
@@ -3706,7 +3706,7 @@
         <v>42671</v>
       </c>
       <c r="B220" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C220">
         <v>0</v>
@@ -3717,7 +3717,7 @@
         <v>42673</v>
       </c>
       <c r="B221" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C221">
         <v>1</v>
@@ -3728,7 +3728,7 @@
         <v>42674</v>
       </c>
       <c r="B222" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C222">
         <v>1</v>
@@ -3739,7 +3739,7 @@
         <v>42675</v>
       </c>
       <c r="B223" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C223">
         <v>1</v>
@@ -3750,7 +3750,7 @@
         <v>42688</v>
       </c>
       <c r="B224" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C224">
         <v>1</v>
@@ -3761,7 +3761,7 @@
         <v>42716</v>
       </c>
       <c r="B225" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C225">
         <v>1</v>
@@ -3772,7 +3772,7 @@
         <v>42717</v>
       </c>
       <c r="B226" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>42729</v>
       </c>
       <c r="B227" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C227">
         <v>1</v>
@@ -3794,7 +3794,7 @@
         <v>42736</v>
       </c>
       <c r="B228" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C228">
         <v>1</v>
@@ -3805,7 +3805,7 @@
         <v>42749</v>
       </c>
       <c r="B229" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C229">
         <v>1</v>
@@ -3816,7 +3816,7 @@
         <v>42761</v>
       </c>
       <c r="B230" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C230">
         <v>1</v>
@@ -3827,7 +3827,7 @@
         <v>42785</v>
       </c>
       <c r="B231" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -3838,7 +3838,7 @@
         <v>42790</v>
       </c>
       <c r="B232" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C232">
         <v>1</v>
@@ -3849,7 +3849,7 @@
         <v>42807</v>
       </c>
       <c r="B233" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C233">
         <v>1</v>
@@ -3860,7 +3860,7 @@
         <v>42822</v>
       </c>
       <c r="B234" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C234">
         <v>1</v>
@@ -3871,7 +3871,7 @@
         <v>42829</v>
       </c>
       <c r="B235" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C235">
         <v>0</v>
@@ -3882,7 +3882,7 @@
         <v>42834</v>
       </c>
       <c r="B236" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -3893,7 +3893,7 @@
         <v>42836</v>
       </c>
       <c r="B237" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C237">
         <v>0</v>
@@ -3904,7 +3904,7 @@
         <v>43190</v>
       </c>
       <c r="B238" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -3915,7 +3915,7 @@
         <v>42839</v>
       </c>
       <c r="B239" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C239">
         <v>1</v>
@@ -3926,7 +3926,7 @@
         <v>42839</v>
       </c>
       <c r="B240" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C240">
         <v>0</v>
@@ -3937,7 +3937,7 @@
         <v>42856</v>
       </c>
       <c r="B241" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C241">
         <v>1</v>
@@ -3948,7 +3948,7 @@
         <v>42865</v>
       </c>
       <c r="B242" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C242">
         <v>0</v>
@@ -3959,7 +3959,7 @@
         <v>42912</v>
       </c>
       <c r="B243" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C243">
         <v>1</v>
@@ -3970,7 +3970,7 @@
         <v>42954</v>
       </c>
       <c r="B244" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C244">
         <v>1</v>
@@ -3981,7 +3981,7 @@
         <v>42962</v>
       </c>
       <c r="B245" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C245">
         <v>1</v>
@@ -3992,7 +3992,7 @@
         <v>42962</v>
       </c>
       <c r="B246" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C246">
         <v>1</v>
@@ -4003,7 +4003,7 @@
         <v>42964</v>
       </c>
       <c r="B247" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C247">
         <v>1</v>
@@ -4014,7 +4014,7 @@
         <v>42972</v>
       </c>
       <c r="B248" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C248">
         <v>1</v>
@@ -4025,7 +4025,7 @@
         <v>42973</v>
       </c>
       <c r="B249" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C249">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>42974</v>
       </c>
       <c r="B250" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C250">
         <v>0</v>
@@ -4047,7 +4047,7 @@
         <v>42975</v>
       </c>
       <c r="B251" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -4058,7 +4058,7 @@
         <v>42976</v>
       </c>
       <c r="B252" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C252">
         <v>0</v>
@@ -4069,13 +4069,13 @@
         <v>42976</v>
       </c>
       <c r="B253" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C253">
         <v>0</v>
       </c>
       <c r="D253" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
@@ -4083,7 +4083,7 @@
         <v>42977</v>
       </c>
       <c r="B254" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C254">
         <v>0</v>
@@ -4094,7 +4094,7 @@
         <v>42978</v>
       </c>
       <c r="B255" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C255">
         <v>0</v>
@@ -4105,7 +4105,7 @@
         <v>42979</v>
       </c>
       <c r="B256" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -4116,7 +4116,7 @@
         <v>42980</v>
       </c>
       <c r="B257" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C257">
         <v>1</v>
@@ -4127,7 +4127,7 @@
         <v>42980</v>
       </c>
       <c r="B258" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C258">
         <v>0</v>
@@ -4138,7 +4138,7 @@
         <v>42983</v>
       </c>
       <c r="B259" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C259">
         <v>1</v>
@@ -4149,13 +4149,13 @@
         <v>42997</v>
       </c>
       <c r="B260" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C260">
         <v>0</v>
       </c>
       <c r="D260" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
@@ -4163,7 +4163,7 @@
         <v>42999</v>
       </c>
       <c r="B261" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -4174,7 +4174,7 @@
         <v>43000</v>
       </c>
       <c r="B262" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C262">
         <v>0</v>
@@ -4185,7 +4185,7 @@
         <v>43001</v>
       </c>
       <c r="B263" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C263">
         <v>0</v>
@@ -4196,7 +4196,7 @@
         <v>43002</v>
       </c>
       <c r="B264" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C264">
         <v>0</v>
@@ -4207,7 +4207,7 @@
         <v>43003</v>
       </c>
       <c r="B265" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C265">
         <v>0</v>
@@ -4218,7 +4218,7 @@
         <v>43004</v>
       </c>
       <c r="B266" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -4229,7 +4229,7 @@
         <v>43005</v>
       </c>
       <c r="B267" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C267">
         <v>0</v>
@@ -4240,7 +4240,7 @@
         <v>43006</v>
       </c>
       <c r="B268" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -4251,7 +4251,7 @@
         <v>43007</v>
       </c>
       <c r="B269" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C269">
         <v>0</v>
@@ -4262,7 +4262,7 @@
         <v>43008</v>
       </c>
       <c r="B270" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C270">
         <v>1</v>
@@ -4273,7 +4273,7 @@
         <v>43009</v>
       </c>
       <c r="B271" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C271">
         <v>1</v>
@@ -4284,7 +4284,7 @@
         <v>43010</v>
       </c>
       <c r="B272" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C272">
         <v>1</v>
@@ -4295,7 +4295,7 @@
         <v>43025</v>
       </c>
       <c r="B273" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C273">
         <v>0</v>
@@ -4306,7 +4306,7 @@
         <v>43027</v>
       </c>
       <c r="B274" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C274">
         <v>1</v>
@@ -4317,7 +4317,7 @@
         <v>43028</v>
       </c>
       <c r="B275" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C275">
         <v>1</v>
@@ -4328,7 +4328,7 @@
         <v>43029</v>
       </c>
       <c r="B276" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C276">
         <v>1</v>
@@ -4339,7 +4339,7 @@
         <v>43043</v>
       </c>
       <c r="B277" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C277">
         <v>1</v>
@@ -4350,7 +4350,7 @@
         <v>43070</v>
       </c>
       <c r="B278" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C278">
         <v>1</v>
@@ -4361,7 +4361,7 @@
         <v>43072</v>
       </c>
       <c r="B279" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C279">
         <v>0</v>
@@ -4372,7 +4372,7 @@
         <v>43094</v>
       </c>
       <c r="B280" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C280">
         <v>1</v>
@@ -4383,7 +4383,7 @@
         <v>43101</v>
       </c>
       <c r="B281" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C281">
         <v>1</v>
@@ -4394,7 +4394,7 @@
         <v>43114</v>
       </c>
       <c r="B282" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C282">
         <v>1</v>
@@ -4405,7 +4405,7 @@
         <v>43126</v>
       </c>
       <c r="B283" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C283">
         <v>1</v>
@@ -4416,7 +4416,7 @@
         <v>43144</v>
       </c>
       <c r="B284" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C284">
         <v>1</v>
@@ -4427,7 +4427,7 @@
         <v>43150</v>
       </c>
       <c r="B285" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C285">
         <v>0</v>
@@ -4438,7 +4438,7 @@
         <v>43161</v>
       </c>
       <c r="B286" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C286">
         <v>1</v>
@@ -4449,7 +4449,7 @@
         <v>43177</v>
       </c>
       <c r="B287" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C287">
         <v>1</v>
@@ -4460,7 +4460,7 @@
         <v>43184</v>
       </c>
       <c r="B288" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C288">
         <v>0</v>
@@ -4471,7 +4471,7 @@
         <v>43188</v>
       </c>
       <c r="B289" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C289">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>43189</v>
       </c>
       <c r="B290" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C290">
         <v>1</v>
@@ -4493,7 +4493,7 @@
         <v>43204</v>
       </c>
       <c r="B291" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C291">
         <v>0</v>
@@ -4504,7 +4504,7 @@
         <v>43220</v>
       </c>
       <c r="B292" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C292">
         <v>0</v>
@@ -4515,7 +4515,7 @@
         <v>43221</v>
       </c>
       <c r="B293" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C293">
         <v>1</v>
@@ -4526,13 +4526,13 @@
         <v>43252</v>
       </c>
       <c r="B294" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C294">
         <v>0</v>
       </c>
       <c r="D294" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
@@ -4540,13 +4540,13 @@
         <v>43253</v>
       </c>
       <c r="B295" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C295">
         <v>0</v>
       </c>
       <c r="D295" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
@@ -4554,13 +4554,13 @@
         <v>43263</v>
       </c>
       <c r="B296" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C296">
         <v>0</v>
       </c>
       <c r="D296" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
@@ -4568,7 +4568,7 @@
         <v>43267</v>
       </c>
       <c r="B297" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C297">
         <v>1</v>
@@ -4579,13 +4579,13 @@
         <v>43276</v>
       </c>
       <c r="B298" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C298">
         <v>0</v>
       </c>
       <c r="D298" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
@@ -4593,13 +4593,13 @@
         <v>43283</v>
       </c>
       <c r="B299" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C299">
         <v>0</v>
       </c>
       <c r="D299" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
@@ -4607,13 +4607,13 @@
         <v>43284</v>
       </c>
       <c r="B300" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C300">
         <v>0</v>
       </c>
       <c r="D300" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
@@ -4621,13 +4621,13 @@
         <v>43289</v>
       </c>
       <c r="B301" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C301">
         <v>0</v>
       </c>
       <c r="D301" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
@@ -4635,13 +4635,13 @@
         <v>43290</v>
       </c>
       <c r="B302" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C302">
         <v>0</v>
       </c>
       <c r="D302" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
@@ -4649,13 +4649,13 @@
         <v>43291</v>
       </c>
       <c r="B303" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C303">
         <v>0</v>
       </c>
       <c r="D303" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
@@ -4663,13 +4663,13 @@
         <v>43306</v>
       </c>
       <c r="B304" t="s">
+        <v>71</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304" t="s">
         <v>72</v>
-      </c>
-      <c r="C304">
-        <v>0</v>
-      </c>
-      <c r="D304" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
@@ -4677,13 +4677,13 @@
         <v>43321</v>
       </c>
       <c r="B305" t="s">
+        <v>71</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305" t="s">
         <v>72</v>
-      </c>
-      <c r="C305">
-        <v>0</v>
-      </c>
-      <c r="D305" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
@@ -4691,7 +4691,7 @@
         <v>43327</v>
       </c>
       <c r="B306" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C306">
         <v>1</v>
@@ -4702,7 +4702,7 @@
         <v>43329</v>
       </c>
       <c r="B307" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C307">
         <v>1</v>
@@ -4713,13 +4713,13 @@
         <v>43329</v>
       </c>
       <c r="B308" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C308">
         <v>0</v>
       </c>
       <c r="D308" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
@@ -4727,7 +4727,7 @@
         <v>43334</v>
       </c>
       <c r="B309" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C309">
         <v>1</v>
@@ -4738,7 +4738,7 @@
         <v>43338</v>
       </c>
       <c r="B310" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C310">
         <v>1</v>
@@ -4749,7 +4749,7 @@
         <v>43345</v>
       </c>
       <c r="B311" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C311">
         <v>1</v>
@@ -4760,13 +4760,13 @@
         <v>43353</v>
       </c>
       <c r="B312" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C312">
         <v>0</v>
       </c>
       <c r="D312" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
@@ -4774,7 +4774,7 @@
         <v>43355</v>
       </c>
       <c r="B313" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C313">
         <v>0</v>
@@ -4785,7 +4785,7 @@
         <v>43356</v>
       </c>
       <c r="B314" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C314">
         <v>1</v>
@@ -4796,7 +4796,7 @@
         <v>43357</v>
       </c>
       <c r="B315" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C315">
         <v>0</v>
@@ -4807,7 +4807,7 @@
         <v>43358</v>
       </c>
       <c r="B316" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C316">
         <v>0</v>
@@ -4818,7 +4818,7 @@
         <v>43359</v>
       </c>
       <c r="B317" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C317">
         <v>0</v>
@@ -4829,7 +4829,7 @@
         <v>43360</v>
       </c>
       <c r="B318" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C318">
         <v>0</v>
@@ -4840,7 +4840,7 @@
         <v>43361</v>
       </c>
       <c r="B319" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C319">
         <v>0</v>
@@ -4851,7 +4851,7 @@
         <v>43362</v>
       </c>
       <c r="B320" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -4862,7 +4862,7 @@
         <v>43363</v>
       </c>
       <c r="B321" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C321">
         <v>0</v>
@@ -4873,7 +4873,7 @@
         <v>43363</v>
       </c>
       <c r="B322" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C322">
         <v>1</v>
@@ -4884,7 +4884,7 @@
         <v>43364</v>
       </c>
       <c r="B323" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C323">
         <v>0</v>
@@ -4895,7 +4895,7 @@
         <v>43365</v>
       </c>
       <c r="B324" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C324">
         <v>0</v>
@@ -4906,7 +4906,7 @@
         <v>43366</v>
       </c>
       <c r="B325" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C325">
         <v>1</v>
@@ -4917,7 +4917,7 @@
         <v>43375</v>
       </c>
       <c r="B326" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C326">
         <v>1</v>
@@ -4928,7 +4928,7 @@
         <v>43383</v>
       </c>
       <c r="B327" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C327">
         <v>0</v>
@@ -4939,7 +4939,7 @@
         <v>43384</v>
       </c>
       <c r="B328" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C328">
         <v>0</v>
@@ -4950,7 +4950,7 @@
         <v>43385</v>
       </c>
       <c r="B329" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C329">
         <v>0</v>
@@ -4961,7 +4961,7 @@
         <v>43386</v>
       </c>
       <c r="B330" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C330">
         <v>0</v>
@@ -4972,7 +4972,7 @@
         <v>43387</v>
       </c>
       <c r="B331" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C331">
         <v>0</v>
@@ -4983,7 +4983,7 @@
         <v>43388</v>
       </c>
       <c r="B332" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C332">
         <v>0</v>
@@ -4994,7 +4994,7 @@
         <v>43389</v>
       </c>
       <c r="B333" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C333">
         <v>0</v>
@@ -5005,7 +5005,7 @@
         <v>43390</v>
       </c>
       <c r="B334" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C334">
         <v>0</v>
@@ -5016,7 +5016,7 @@
         <v>43391</v>
       </c>
       <c r="B335" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C335">
         <v>1</v>
@@ -5027,7 +5027,7 @@
         <v>43409</v>
       </c>
       <c r="B336" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C336">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>43411</v>
       </c>
       <c r="B337" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C337">
         <v>1</v>
@@ -5049,7 +5049,7 @@
         <v>43412</v>
       </c>
       <c r="B338" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C338">
         <v>1</v>
@@ -5060,7 +5060,7 @@
         <v>43413</v>
       </c>
       <c r="B339" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C339">
         <v>1</v>
@@ -5071,7 +5071,7 @@
         <v>43424</v>
       </c>
       <c r="B340" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C340">
         <v>1</v>
@@ -5082,7 +5082,7 @@
         <v>43427</v>
       </c>
       <c r="B341" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C341">
         <v>1</v>
@@ -5093,7 +5093,7 @@
         <v>43456</v>
       </c>
       <c r="B342" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C342">
         <v>0</v>
@@ -5104,7 +5104,7 @@
         <v>43459</v>
       </c>
       <c r="B343" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C343">
         <v>1</v>
@@ -5115,7 +5115,7 @@
         <v>43466</v>
       </c>
       <c r="B344" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C344">
         <v>1</v>
@@ -5126,7 +5126,7 @@
         <v>43479</v>
       </c>
       <c r="B345" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C345">
         <v>1</v>
@@ -5137,7 +5137,7 @@
         <v>43491</v>
       </c>
       <c r="B346" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C346">
         <v>1</v>
@@ -5148,7 +5148,7 @@
         <v>43515</v>
       </c>
       <c r="B347" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C347">
         <v>0</v>
@@ -5159,7 +5159,7 @@
         <v>43528</v>
       </c>
       <c r="B348" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C348">
         <v>1</v>
@@ -5170,7 +5170,7 @@
         <v>43545</v>
       </c>
       <c r="B349" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C349">
         <v>1</v>
@@ -5181,7 +5181,7 @@
         <v>43561</v>
       </c>
       <c r="B350" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C350">
         <v>1</v>
@@ -5192,7 +5192,7 @@
         <v>43569</v>
       </c>
       <c r="B351" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C351">
         <v>1</v>
@@ -5203,7 +5203,7 @@
         <v>43569</v>
       </c>
       <c r="B352" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C352">
         <v>0</v>
@@ -5214,7 +5214,7 @@
         <v>43572</v>
       </c>
       <c r="B353" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C353">
         <v>0</v>
@@ -5225,7 +5225,7 @@
         <v>43574</v>
       </c>
       <c r="B354" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C354">
         <v>1</v>
@@ -5236,7 +5236,7 @@
         <v>43574</v>
       </c>
       <c r="B355" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C355">
         <v>0</v>
@@ -5247,7 +5247,7 @@
         <v>43584</v>
       </c>
       <c r="B356" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C356">
         <v>1</v>
@@ -5258,7 +5258,7 @@
         <v>43586</v>
       </c>
       <c r="B357" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C357">
         <v>1</v>
@@ -5269,7 +5269,7 @@
         <v>43603</v>
       </c>
       <c r="B358" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C358">
         <v>0</v>
@@ -5280,7 +5280,7 @@
         <v>43621</v>
       </c>
       <c r="B359" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C359">
         <v>1</v>
@@ -5291,7 +5291,7 @@
         <v>43647</v>
       </c>
       <c r="B360" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C360">
         <v>0</v>
@@ -5302,13 +5302,13 @@
         <v>43648</v>
       </c>
       <c r="B361" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C361">
         <v>0</v>
       </c>
       <c r="D361" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.2">
@@ -5316,13 +5316,13 @@
         <v>43680</v>
       </c>
       <c r="B362" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C362">
         <v>0</v>
       </c>
       <c r="D362" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
@@ -5330,13 +5330,13 @@
         <v>43681</v>
       </c>
       <c r="B363" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C363">
         <v>0</v>
       </c>
       <c r="D363" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.2">
@@ -5344,7 +5344,7 @@
         <v>43689</v>
       </c>
       <c r="B364" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C364">
         <v>1</v>
@@ -5355,7 +5355,7 @@
         <v>43692</v>
       </c>
       <c r="B365" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C365">
         <v>1</v>
@@ -5366,7 +5366,7 @@
         <v>43692</v>
       </c>
       <c r="B366" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C366">
         <v>1</v>
@@ -5377,7 +5377,7 @@
         <v>43694</v>
       </c>
       <c r="B367" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C367">
         <v>1</v>
@@ -5388,7 +5388,7 @@
         <v>43701</v>
       </c>
       <c r="B368" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C368">
         <v>1</v>
@@ -5399,7 +5399,7 @@
         <v>43710</v>
       </c>
       <c r="B369" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C369">
         <v>1</v>
@@ -5410,7 +5410,7 @@
         <v>43711</v>
       </c>
       <c r="B370" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C370">
         <v>0</v>
@@ -5421,7 +5421,7 @@
         <v>43712</v>
       </c>
       <c r="B371" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C371">
         <v>0</v>
@@ -5432,13 +5432,13 @@
         <v>43712</v>
       </c>
       <c r="B372" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C372">
         <v>0</v>
       </c>
       <c r="D372" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.2">
@@ -5446,7 +5446,7 @@
         <v>43713</v>
       </c>
       <c r="B373" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C373">
         <v>0</v>
@@ -5457,13 +5457,13 @@
         <v>43713</v>
       </c>
       <c r="B374" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C374">
         <v>0</v>
       </c>
       <c r="D374" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
@@ -5471,7 +5471,7 @@
         <v>43714</v>
       </c>
       <c r="B375" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C375">
         <v>0</v>
@@ -5482,7 +5482,7 @@
         <v>43715</v>
       </c>
       <c r="B376" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C376">
         <v>0</v>
@@ -5493,13 +5493,13 @@
         <v>43715</v>
       </c>
       <c r="B377" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C377">
         <v>1</v>
       </c>
       <c r="D377" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.2">
@@ -5507,7 +5507,7 @@
         <v>43716</v>
       </c>
       <c r="B378" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C378">
         <v>0</v>
@@ -5518,7 +5518,7 @@
         <v>43717</v>
       </c>
       <c r="B379" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C379">
         <v>0</v>
@@ -5529,7 +5529,7 @@
         <v>43718</v>
       </c>
       <c r="B380" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C380">
         <v>0</v>
@@ -5540,7 +5540,7 @@
         <v>43718</v>
       </c>
       <c r="B381" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C381">
         <v>1</v>
@@ -5551,7 +5551,7 @@
         <v>43719</v>
       </c>
       <c r="B382" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C382">
         <v>0</v>
@@ -5562,7 +5562,7 @@
         <v>43720</v>
       </c>
       <c r="B383" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C383">
         <v>1</v>
@@ -5573,7 +5573,7 @@
         <v>43737</v>
       </c>
       <c r="B384" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C384">
         <v>0</v>
@@ -5584,7 +5584,7 @@
         <v>43738</v>
       </c>
       <c r="B385" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C385">
         <v>0</v>
@@ -5595,7 +5595,7 @@
         <v>43739</v>
       </c>
       <c r="B386" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C386">
         <v>0</v>
@@ -5606,7 +5606,7 @@
         <v>43740</v>
       </c>
       <c r="B387" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C387">
         <v>1</v>
@@ -5617,7 +5617,7 @@
         <v>43740</v>
       </c>
       <c r="B388" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C388">
         <v>0</v>
@@ -5628,7 +5628,7 @@
         <v>43741</v>
       </c>
       <c r="B389" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C389">
         <v>0</v>
@@ -5639,7 +5639,7 @@
         <v>43742</v>
       </c>
       <c r="B390" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C390">
         <v>0</v>
@@ -5650,7 +5650,7 @@
         <v>43743</v>
       </c>
       <c r="B391" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C391">
         <v>0</v>
@@ -5661,7 +5661,7 @@
         <v>43744</v>
       </c>
       <c r="B392" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C392">
         <v>0</v>
@@ -5672,7 +5672,7 @@
         <v>43745</v>
       </c>
       <c r="B393" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C393">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>43746</v>
       </c>
       <c r="B394" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C394">
         <v>1</v>
@@ -5694,7 +5694,7 @@
         <v>43759</v>
       </c>
       <c r="B395" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C395">
         <v>1</v>
@@ -5705,7 +5705,7 @@
         <v>43763</v>
       </c>
       <c r="B396" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C396">
         <v>0</v>
@@ -5716,7 +5716,7 @@
         <v>43765</v>
       </c>
       <c r="B397" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C397">
         <v>1</v>
@@ -5727,7 +5727,7 @@
         <v>43766</v>
       </c>
       <c r="B398" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C398">
         <v>1</v>
@@ -5738,7 +5738,7 @@
         <v>43767</v>
       </c>
       <c r="B399" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C399">
         <v>1</v>
@@ -5749,7 +5749,7 @@
         <v>43779</v>
       </c>
       <c r="B400" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C400">
         <v>1</v>
@@ -5760,7 +5760,7 @@
         <v>43781</v>
       </c>
       <c r="B401" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C401">
         <v>1</v>
@@ -5771,7 +5771,7 @@
         <v>43810</v>
       </c>
       <c r="B402" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C402">
         <v>0</v>
@@ -5782,13 +5782,13 @@
         <v>43824</v>
       </c>
       <c r="B403" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C403">
         <v>1</v>
       </c>
       <c r="D403" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.2">
@@ -5796,13 +5796,13 @@
         <v>43825</v>
       </c>
       <c r="B404" t="s">
+        <v>83</v>
+      </c>
+      <c r="C404">
+        <v>0</v>
+      </c>
+      <c r="D404" t="s">
         <v>84</v>
-      </c>
-      <c r="C404">
-        <v>0</v>
-      </c>
-      <c r="D404" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.2">
@@ -5810,7 +5810,7 @@
         <v>43831</v>
       </c>
       <c r="B405" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C405">
         <v>1</v>
@@ -5821,7 +5821,7 @@
         <v>43845</v>
       </c>
       <c r="B406" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C406">
         <v>1</v>
@@ -5832,13 +5832,13 @@
         <v>43854</v>
       </c>
       <c r="B407" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C407">
         <v>0</v>
       </c>
       <c r="D407" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.2">
@@ -5846,7 +5846,7 @@
         <v>43856</v>
       </c>
       <c r="B408" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C408">
         <v>1</v>
@@ -5857,7 +5857,7 @@
         <v>43880</v>
       </c>
       <c r="B409" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C409">
         <v>0</v>
@@ -5868,7 +5868,7 @@
         <v>43882</v>
       </c>
       <c r="B410" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C410">
         <v>1</v>
@@ -5879,7 +5879,7 @@
         <v>43900</v>
       </c>
       <c r="B411" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C411">
         <v>1</v>
@@ -5890,13 +5890,13 @@
         <v>43912</v>
       </c>
       <c r="B412" t="s">
+        <v>86</v>
+      </c>
+      <c r="C412">
+        <v>0</v>
+      </c>
+      <c r="D412" t="s">
         <v>87</v>
-      </c>
-      <c r="C412">
-        <v>0</v>
-      </c>
-      <c r="D412" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.2">
@@ -5904,7 +5904,7 @@
         <v>43915</v>
       </c>
       <c r="B413" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C413">
         <v>1</v>
@@ -5915,7 +5915,7 @@
         <v>43923</v>
       </c>
       <c r="B414" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C414">
         <v>0</v>
@@ -5926,7 +5926,7 @@
         <v>43927</v>
       </c>
       <c r="B415" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C415">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>43929</v>
       </c>
       <c r="B416" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C416">
         <v>0</v>
@@ -5948,7 +5948,7 @@
         <v>43931</v>
       </c>
       <c r="B417" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C417">
         <v>1</v>
@@ -5959,7 +5959,7 @@
         <v>43935</v>
       </c>
       <c r="B418" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C418">
         <v>1</v>
@@ -5970,7 +5970,7 @@
         <v>43946</v>
       </c>
       <c r="B419" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C419">
         <v>0</v>
@@ -5981,7 +5981,7 @@
         <v>43952</v>
       </c>
       <c r="B420" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C420">
         <v>1</v>
@@ -5992,7 +5992,7 @@
         <v>43958</v>
       </c>
       <c r="B421" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C421">
         <v>0</v>
@@ -6003,7 +6003,7 @@
         <v>43976</v>
       </c>
       <c r="B422" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C422">
         <v>1</v>
@@ -6014,7 +6014,7 @@
         <v>43985</v>
       </c>
       <c r="B423" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C423">
         <v>0</v>
@@ -6025,7 +6025,7 @@
         <v>44043</v>
       </c>
       <c r="B424" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C424">
         <v>1</v>
@@ -6036,7 +6036,7 @@
         <v>44046</v>
       </c>
       <c r="B425" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C425">
         <v>1</v>
@@ -6047,7 +6047,7 @@
         <v>44054</v>
       </c>
       <c r="B426" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C426">
         <v>1</v>
@@ -6058,7 +6058,7 @@
         <v>44058</v>
       </c>
       <c r="B427" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C427">
         <v>1</v>
@@ -6069,7 +6069,7 @@
         <v>44060</v>
       </c>
       <c r="B428" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C428">
         <v>1</v>
@@ -6080,7 +6080,7 @@
         <v>44064</v>
       </c>
       <c r="B429" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C429">
         <v>1</v>
@@ -6091,7 +6091,7 @@
         <v>44065</v>
       </c>
       <c r="B430" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C430">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         <v>44066</v>
       </c>
       <c r="B431" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C431">
         <v>0</v>
@@ -6113,7 +6113,7 @@
         <v>44067</v>
       </c>
       <c r="B432" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C432">
         <v>0</v>
@@ -6124,7 +6124,7 @@
         <v>44068</v>
       </c>
       <c r="B433" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C433">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>44069</v>
       </c>
       <c r="B434" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C434">
         <v>0</v>
@@ -6146,7 +6146,7 @@
         <v>44070</v>
       </c>
       <c r="B435" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C435">
         <v>0</v>
@@ -6157,7 +6157,7 @@
         <v>44071</v>
       </c>
       <c r="B436" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C436">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         <v>44072</v>
       </c>
       <c r="B437" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C437">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>44073</v>
       </c>
       <c r="B438" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C438">
         <v>0</v>
@@ -6190,7 +6190,7 @@
         <v>44074</v>
       </c>
       <c r="B439" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C439">
         <v>0</v>
@@ -6201,7 +6201,7 @@
         <v>44075</v>
       </c>
       <c r="B440" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C440">
         <v>1</v>
@@ -6212,7 +6212,7 @@
         <v>44106</v>
       </c>
       <c r="B441" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C441">
         <v>1</v>
@@ -6223,13 +6223,13 @@
         <v>44116</v>
       </c>
       <c r="B442" t="s">
+        <v>89</v>
+      </c>
+      <c r="C442">
+        <v>0</v>
+      </c>
+      <c r="D442" t="s">
         <v>90</v>
-      </c>
-      <c r="C442">
-        <v>0</v>
-      </c>
-      <c r="D442" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.2">
@@ -6237,7 +6237,7 @@
         <v>44121</v>
       </c>
       <c r="B443" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C443">
         <v>0</v>
@@ -6248,7 +6248,7 @@
         <v>44122</v>
       </c>
       <c r="B444" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C444">
         <v>0</v>
@@ -6259,7 +6259,7 @@
         <v>44123</v>
       </c>
       <c r="B445" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C445">
         <v>0</v>
@@ -6270,7 +6270,7 @@
         <v>44124</v>
       </c>
       <c r="B446" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C446">
         <v>0</v>
@@ -6281,7 +6281,7 @@
         <v>44125</v>
       </c>
       <c r="B447" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C447">
         <v>0</v>
@@ -6292,7 +6292,7 @@
         <v>44126</v>
       </c>
       <c r="B448" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C448">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>44127</v>
       </c>
       <c r="B449" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C449">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>44128</v>
       </c>
       <c r="B450" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C450">
         <v>0</v>
@@ -6325,7 +6325,7 @@
         <v>44129</v>
       </c>
       <c r="B451" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C451">
         <v>1</v>
@@ -6336,7 +6336,7 @@
         <v>44133</v>
       </c>
       <c r="B452" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C452">
         <v>1</v>
@@ -6347,13 +6347,13 @@
         <v>44140</v>
       </c>
       <c r="B453" t="s">
+        <v>91</v>
+      </c>
+      <c r="C453">
+        <v>0</v>
+      </c>
+      <c r="D453" t="s">
         <v>92</v>
-      </c>
-      <c r="C453">
-        <v>0</v>
-      </c>
-      <c r="D453" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.2">
@@ -6361,7 +6361,7 @@
         <v>44148</v>
       </c>
       <c r="B454" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C454">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>44149</v>
       </c>
       <c r="B455" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C455">
         <v>1</v>
@@ -6383,7 +6383,7 @@
         <v>44150</v>
       </c>
       <c r="B456" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C456">
         <v>1</v>
@@ -6394,7 +6394,7 @@
         <v>44151</v>
       </c>
       <c r="B457" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C457">
         <v>1</v>
@@ -6405,7 +6405,7 @@
         <v>44165</v>
       </c>
       <c r="B458" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C458">
         <v>1</v>
@@ -6416,7 +6416,7 @@
         <v>44190</v>
       </c>
       <c r="B459" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C459">
         <v>1</v>
@@ -6427,7 +6427,7 @@
         <v>44194</v>
       </c>
       <c r="B460" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C460">
         <v>0</v>
@@ -6438,7 +6438,7 @@
         <v>44197</v>
       </c>
       <c r="B461" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C461">
         <v>1</v>
@@ -6449,7 +6449,7 @@
         <v>44211</v>
       </c>
       <c r="B462" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C462">
         <v>1</v>
@@ -6460,7 +6460,7 @@
         <v>44222</v>
       </c>
       <c r="B463" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C463">
         <v>1</v>
@@ -6471,13 +6471,13 @@
         <v>44228</v>
       </c>
       <c r="B464" t="s">
+        <v>93</v>
+      </c>
+      <c r="C464">
+        <v>0</v>
+      </c>
+      <c r="D464" t="s">
         <v>94</v>
-      </c>
-      <c r="C464">
-        <v>0</v>
-      </c>
-      <c r="D464" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.2">
@@ -6485,13 +6485,13 @@
         <v>44228</v>
       </c>
       <c r="B465" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C465">
         <v>0</v>
       </c>
       <c r="D465" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.2">
@@ -6499,7 +6499,7 @@
         <v>44246</v>
       </c>
       <c r="B466" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C466">
         <v>0</v>
@@ -6510,7 +6510,7 @@
         <v>44266</v>
       </c>
       <c r="B467" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C467">
         <v>1</v>
@@ -6521,7 +6521,7 @@
         <v>44284</v>
       </c>
       <c r="B468" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C468">
         <v>1</v>
@@ -6532,7 +6532,7 @@
         <v>44288</v>
       </c>
       <c r="B469" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C469">
         <v>1</v>
@@ -6543,7 +6543,7 @@
         <v>44299</v>
       </c>
       <c r="B470" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C470">
         <v>1</v>
@@ -6554,7 +6554,7 @@
         <v>44300</v>
       </c>
       <c r="B471" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C471">
         <v>1</v>
@@ -6565,7 +6565,7 @@
         <v>44307</v>
       </c>
       <c r="B472" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C472">
         <v>0</v>
@@ -6576,627 +6576,220 @@
         <v>44313</v>
       </c>
       <c r="B473" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C473">
         <v>0</v>
       </c>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A474" s="1">
-        <v>44317</v>
+      <c r="A474" t="s">
+        <v>96</v>
       </c>
       <c r="B474" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="C474">
         <v>1</v>
       </c>
+      <c r="D474" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A475" s="1">
-        <v>44330</v>
+      <c r="A475" t="s">
+        <v>99</v>
       </c>
       <c r="B475" t="s">
-        <v>23</v>
+        <v>100</v>
       </c>
       <c r="C475">
         <v>1</v>
       </c>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A476" s="1">
-        <v>44342</v>
+      <c r="A476" t="s">
+        <v>101</v>
       </c>
       <c r="B476" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="C476">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="D476" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A477" s="1">
-        <v>44398</v>
+      <c r="A477" t="s">
+        <v>104</v>
       </c>
       <c r="B477" t="s">
-        <v>49</v>
+        <v>105</v>
       </c>
       <c r="C477">
         <v>1</v>
       </c>
+      <c r="D477" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A478" s="1">
-        <v>44423</v>
+      <c r="A478" t="s">
+        <v>107</v>
       </c>
       <c r="B478" t="s">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="C478">
         <v>1</v>
       </c>
+      <c r="D478" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A479" s="1">
-        <v>44424</v>
+      <c r="A479" t="s">
+        <v>110</v>
       </c>
       <c r="B479" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="C479">
         <v>1</v>
       </c>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A480" s="1">
-        <v>44427</v>
+      <c r="A480" t="s">
+        <v>112</v>
       </c>
       <c r="B480" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="C480">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A481" s="1">
-        <v>44430</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="481" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A481" t="s">
+        <v>114</v>
       </c>
       <c r="B481" t="s">
-        <v>19</v>
+        <v>115</v>
       </c>
       <c r="C481">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A482" s="1">
-        <v>44438</v>
+        <v>0</v>
+      </c>
+      <c r="D481" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="482" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A482" t="s">
+        <v>116</v>
       </c>
       <c r="B482" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="C482">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A483" s="1">
-        <v>44449</v>
+        <v>0</v>
+      </c>
+      <c r="D482" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="483" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A483" t="s">
+        <v>119</v>
       </c>
       <c r="B483" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="C483">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A484" s="1">
-        <v>44450</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="484" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A484" t="s">
+        <v>120</v>
       </c>
       <c r="B484" t="s">
-        <v>25</v>
+        <v>121</v>
       </c>
       <c r="C484">
         <v>0</v>
       </c>
-    </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A485" s="1">
-        <v>44451</v>
+      <c r="D484" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="485" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A485" t="s">
+        <v>123</v>
       </c>
       <c r="B485" t="s">
-        <v>26</v>
+        <v>113</v>
       </c>
       <c r="C485">
         <v>0</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A486" s="1">
-        <v>44452</v>
+    <row r="486" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A486" t="s">
+        <v>124</v>
       </c>
       <c r="B486" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C486">
         <v>0</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A487" s="1">
-        <v>44453</v>
+    <row r="487" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A487" t="s">
+        <v>125</v>
       </c>
       <c r="B487" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="C487">
         <v>0</v>
       </c>
-    </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A488" s="1">
-        <v>44454</v>
+      <c r="D487" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="488" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A488" t="s">
+        <v>128</v>
       </c>
       <c r="B488" t="s">
-        <v>29</v>
+        <v>129</v>
       </c>
       <c r="C488">
         <v>0</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A489" s="1">
-        <v>44455</v>
+    <row r="489" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A489" t="s">
+        <v>130</v>
       </c>
       <c r="B489" t="s">
-        <v>30</v>
+        <v>129</v>
       </c>
       <c r="C489">
         <v>0</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A490" s="1">
-        <v>44456</v>
+    <row r="490" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A490" t="s">
+        <v>131</v>
       </c>
       <c r="B490" t="s">
-        <v>31</v>
+        <v>129</v>
       </c>
       <c r="C490">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A491" s="1">
-        <v>44457</v>
-      </c>
-      <c r="B491" t="s">
-        <v>32</v>
-      </c>
-      <c r="C491">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A492" s="1">
-        <v>44458</v>
-      </c>
-      <c r="B492" t="s">
-        <v>34</v>
-      </c>
-      <c r="C492">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A493" s="1">
-        <v>44471</v>
-      </c>
-      <c r="B493" t="s">
-        <v>40</v>
-      </c>
-      <c r="C493">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A494" s="1">
-        <v>44476</v>
-      </c>
-      <c r="B494" t="s">
-        <v>35</v>
-      </c>
-      <c r="C494">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A495" s="1">
-        <v>44477</v>
-      </c>
-      <c r="B495" t="s">
-        <v>36</v>
-      </c>
-      <c r="C495">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A496" s="1">
-        <v>44478</v>
-      </c>
-      <c r="B496" t="s">
-        <v>37</v>
-      </c>
-      <c r="C496">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="497" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A497" s="1">
-        <v>44479</v>
-      </c>
-      <c r="B497" t="s">
-        <v>38</v>
-      </c>
-      <c r="C497">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="498" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A498" s="1">
-        <v>44480</v>
-      </c>
-      <c r="B498" t="s">
-        <v>39</v>
-      </c>
-      <c r="C498">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="499" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A499" s="1">
-        <v>44481</v>
-      </c>
-      <c r="B499" t="s">
-        <v>41</v>
-      </c>
-      <c r="C499">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="500" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A500" s="1">
-        <v>44482</v>
-      </c>
-      <c r="B500" t="s">
-        <v>42</v>
-      </c>
-      <c r="C500">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="501" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A501" s="1">
-        <v>44483</v>
-      </c>
-      <c r="B501" t="s">
-        <v>60</v>
-      </c>
-      <c r="C501">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="502" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A502" s="1">
-        <v>44484</v>
-      </c>
-      <c r="B502" t="s">
-        <v>44</v>
-      </c>
-      <c r="C502">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="503" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A503" s="1">
-        <v>44488</v>
-      </c>
-      <c r="B503" t="s">
-        <v>7</v>
-      </c>
-      <c r="C503">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="504" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A504" s="1">
-        <v>44502</v>
-      </c>
-      <c r="B504" t="s">
-        <v>45</v>
-      </c>
-      <c r="C504">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="505" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A505" s="1">
-        <v>44504</v>
-      </c>
-      <c r="B505" t="s">
-        <v>46</v>
-      </c>
-      <c r="C505">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="506" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A506" s="1">
-        <v>44505</v>
-      </c>
-      <c r="B506" t="s">
-        <v>82</v>
-      </c>
-      <c r="C506">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="507" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A507" s="1">
-        <v>44506</v>
-      </c>
-      <c r="B507" t="s">
-        <v>48</v>
-      </c>
-      <c r="C507">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="508" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A508" s="1">
-        <v>44519</v>
-      </c>
-      <c r="B508" t="s">
-        <v>50</v>
-      </c>
-      <c r="C508">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="509" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A509" s="1">
-        <v>44548</v>
-      </c>
-      <c r="B509" t="s">
-        <v>52</v>
-      </c>
-      <c r="C509">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="510" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A510" s="1">
-        <v>44555</v>
-      </c>
-      <c r="B510" t="s">
-        <v>53</v>
-      </c>
-      <c r="C510">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="511" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A511" t="s">
-        <v>97</v>
-      </c>
-      <c r="B511" t="s">
-        <v>98</v>
-      </c>
-      <c r="C511">
-        <v>1</v>
-      </c>
-      <c r="D511" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="512" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A512" t="s">
-        <v>100</v>
-      </c>
-      <c r="B512" t="s">
-        <v>101</v>
-      </c>
-      <c r="C512">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="513" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A513" t="s">
-        <v>102</v>
-      </c>
-      <c r="B513" t="s">
-        <v>103</v>
-      </c>
-      <c r="C513">
-        <v>1</v>
-      </c>
-      <c r="D513" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="514" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A514" t="s">
-        <v>105</v>
-      </c>
-      <c r="B514" t="s">
-        <v>106</v>
-      </c>
-      <c r="C514">
-        <v>1</v>
-      </c>
-      <c r="D514" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="515" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A515" t="s">
-        <v>108</v>
-      </c>
-      <c r="B515" t="s">
-        <v>109</v>
-      </c>
-      <c r="C515">
-        <v>1</v>
-      </c>
-      <c r="D515" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="516" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A516" t="s">
-        <v>111</v>
-      </c>
-      <c r="B516" t="s">
-        <v>112</v>
-      </c>
-      <c r="C516">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="517" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A517" t="s">
-        <v>113</v>
-      </c>
-      <c r="B517" t="s">
-        <v>114</v>
-      </c>
-      <c r="C517">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="518" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A518" t="s">
-        <v>115</v>
-      </c>
-      <c r="B518" t="s">
-        <v>116</v>
-      </c>
-      <c r="C518">
-        <v>0</v>
-      </c>
-      <c r="D518" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="519" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A519" t="s">
-        <v>117</v>
-      </c>
-      <c r="B519" t="s">
-        <v>118</v>
-      </c>
-      <c r="C519">
-        <v>0</v>
-      </c>
-      <c r="D519" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="520" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A520" t="s">
-        <v>120</v>
-      </c>
-      <c r="B520" t="s">
-        <v>114</v>
-      </c>
-      <c r="C520">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="521" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A521" t="s">
-        <v>121</v>
-      </c>
-      <c r="B521" t="s">
-        <v>122</v>
-      </c>
-      <c r="C521">
-        <v>0</v>
-      </c>
-      <c r="D521" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="522" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A522" t="s">
-        <v>124</v>
-      </c>
-      <c r="B522" t="s">
-        <v>114</v>
-      </c>
-      <c r="C522">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="523" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A523" t="s">
-        <v>125</v>
-      </c>
-      <c r="B523" t="s">
-        <v>114</v>
-      </c>
-      <c r="C523">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="524" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A524" t="s">
-        <v>126</v>
-      </c>
-      <c r="B524" t="s">
-        <v>127</v>
-      </c>
-      <c r="C524">
-        <v>0</v>
-      </c>
-      <c r="D524" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="525" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A525" t="s">
-        <v>129</v>
-      </c>
-      <c r="B525" t="s">
-        <v>130</v>
-      </c>
-      <c r="C525">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="526" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A526" t="s">
-        <v>131</v>
-      </c>
-      <c r="B526" t="s">
-        <v>130</v>
-      </c>
-      <c r="C526">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="527" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A527" t="s">
-        <v>132</v>
-      </c>
-      <c r="B527" t="s">
-        <v>130</v>
-      </c>
-      <c r="C527">
         <v>0</v>
       </c>
     </row>

--- a/Modified Dataset/Events_Data_1April2013.xlsx
+++ b/Modified Dataset/Events_Data_1April2013.xlsx
@@ -8,14 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arnavgupta/Documents/Arnav/Hackathons/DecodeX/Modified Dataset/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C907860-42E8-C34D-8112-EFB7CEA6A01F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D36552A5-09BF-1E41-88E6-B54087C1142A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1080" yWindow="1140" windowWidth="27640" windowHeight="16540" xr2:uid="{9D46C0F9-12FB-2844-AC27-29D70BA9F9B5}"/>
+    <workbookView xWindow="0" yWindow="10140" windowWidth="27640" windowHeight="16540" xr2:uid="{9D46C0F9-12FB-2844-AC27-29D70BA9F9B5}"/>
   </bookViews>
   <sheets>
     <sheet name="Events_Data" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -561,7 +574,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -741,6 +754,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -902,9 +921,11 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="15" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -6572,13 +6593,13 @@
       </c>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A473" s="1">
+      <c r="A473" s="2">
         <v>44313</v>
       </c>
-      <c r="B473" t="s">
+      <c r="B473" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C473">
+      <c r="C473" s="3">
         <v>0</v>
       </c>
     </row>
